--- a/temp/BBVA_VISA_20250601.xlsx
+++ b/temp/BBVA_VISA_20250601.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,7 +488,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MERPAGO*AXIONENERGY</t>
+          <t>501580K MERPAGO*AXIONENERGY</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>METROGAS SA DEB  040000136346</t>
+          <t>571851* METROGAS SA DEB 040000136346</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AA2000 PKG EZEIZA</t>
+          <t>000001* EDENOR SA 000007691385963</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10500</v>
+        <v>10667.87</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EDENOR SA        000007691385963</t>
+          <t>002004* AA2000 PKG EZEIZA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10667.87</v>
+        <v>10500</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -588,7 +588,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NETFLIX.COM      4821908557765366</t>
+          <t>115109K NETFLIX.COM 482190855 USD 8,53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AUTOPISTAS URBAN 000000004488335</t>
+          <t>000001* AUTOPISTAS URBAN 000000004488335</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MERPAGO*MODAXPRESSBA</t>
+          <t>978934K MERPAGO*ESCUELADAVINCI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>21274.69</v>
+        <v>264400</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MERPAGO*ESCUELADAVINCI</t>
+          <t>751873K MERPAGO*MODAXPRESSBA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>264400</v>
+        <v>21274.69</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PVS*THOMAS KITCHEN AND CO</t>
+          <t>185665K MERPAGO*FARMACITY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5750</v>
+        <v>32199</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MERPAGO*FARMACITY</t>
+          <t>006376* PVS*THOMAS KITCHEN AND CO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>32199</v>
+        <v>5750</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MERPAGO*FARMACITY</t>
+          <t>968318K MERPAGO*FARMACITY</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MERPAGO*FARMACITY</t>
+          <t>977076K MERPAGO*FARMACITY</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>POTTERY COFFEE  DELI-POT</t>
+          <t>789835K POTTERY COFFEE DELI-POT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -808,23 +808,573 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>994344* BBVA SEGUROS A2052000420510-023-000</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>15249.34</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BBVA VISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>2025-06-13</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>PINCHOS-PINCHOS</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>491046K PINCHOS-PINCHOS</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>17200</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>BBVA VISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>010998* TRIUNFO COOP D0000007681097-094-008</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>48118</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>BBVA VISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>007687K PAYU*AR*UBER</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4940</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>BBVA VISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>864313K MERPAGO*VEAEXPRESS</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>64761.72</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>BBVA VISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>000001* AUTOPISTAS URBAN 000000004488335</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>827.35</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>BBVA VISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>287537K MERPAGO*SVMN</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>BBVA VISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>000001* SIRO -ROI SA 079001</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>85102.61</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>BBVA VISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>312341K MERPAGO*HAVANNAFOODLI</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>6600</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>BBVA VISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>595406K MERPAGO*MCDONALDSECOMM</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>24900</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>BBVA VISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>241004F Spotify USD 2,90</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>BBVA VISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>539697K MERPAGO*PILISAR</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>122999</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>BBVA VISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>007115* CINEMARK</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>36900</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>BBVA VISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>626168K MERPAGO*SCANNAPIECO</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>18800</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>BBVA VISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>004439K AXION BONPLAND</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>9382.950000000001</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>BBVA VISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>005932K PEDIDOSYA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>46159</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>BBVA VISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>006726* SANDRULI SRL</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10800</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>BBVA VISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>140716* EXPERTA SEGURO0000037758111-015-000</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>14566.67</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>BBVA VISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>IIBB PERCEP-CABA 2,00%( 10163,49)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>203.26</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>BBVA VISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>IIBB PERCEP-CABA 2,00%( 3455,35)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>BBVA VISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>IVA RG 4240 21%( 10163,49)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2134.33</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>BBVA VISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>IVA RG 4240 21%( 3455,35)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>725.62</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>BBVA VISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>DB.RG 5617 30% ( 13618,84 )</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>4085.65</v>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>BBVA VISA</t>
         </is>

--- a/temp/BBVA_VISA_20250601.xlsx
+++ b/temp/BBVA_VISA_20250601.xlsx
@@ -471,12 +471,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>-1010605.89</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-1010605,89</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -496,12 +498,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>9272.030000000001</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>9272,03</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -521,12 +525,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>4508.02</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4508,02</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -546,12 +552,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>10667.87</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>10667,87</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -571,12 +579,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>10500</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>10500,0</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -596,12 +606,14 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>8.529999999999999</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8,53</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -621,12 +633,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>789.45</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>789,45</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -646,12 +660,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>264400</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>264400,0</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -671,12 +687,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>21274.69</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>21274,69</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -696,12 +714,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>32199</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>32199,0</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -721,12 +741,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>5750</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>5750,0</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -746,12 +768,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>24145</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>24145,0</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -771,12 +795,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>2060</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2060,0</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -796,12 +822,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>17000</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>17000,0</t>
+        </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -821,12 +849,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>15249.34</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>15249,34</t>
+        </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -846,12 +876,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>17200</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>17200,0</t>
+        </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -871,12 +903,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>48118</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>48118,0</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -896,12 +930,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>4940</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>4940,0</t>
+        </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -921,12 +957,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>64761.72</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>64761,72</t>
+        </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -946,12 +984,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>827.35</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>827,35</t>
+        </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -971,12 +1011,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>18000</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>18000,0</t>
+        </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -996,12 +1038,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>85102.61</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>85102,61</t>
+        </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1065,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>6600</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>6600,0</t>
+        </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1092,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>24900</v>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>24900,0</t>
+        </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1119,14 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>2.9</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2,9</t>
+        </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1146,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>122999</v>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>122999,0</t>
+        </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1173,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>36900</v>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>36900,0</t>
+        </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1200,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>18800</v>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>18800,0</t>
+        </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1227,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>9382.950000000001</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>9382,95</t>
+        </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1254,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>46159</v>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>46159,0</t>
+        </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1281,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>10800</v>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>10800,0</t>
+        </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1308,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>14566.67</v>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>14566,67</t>
+        </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1335,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>203.26</v>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>203,26</t>
+        </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1362,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>69.09999999999999</v>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>69,1</t>
+        </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1389,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>2134.33</v>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2134,33</t>
+        </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1416,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>725.62</v>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>725,62</t>
+        </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1443,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>4085.65</v>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>4085,65</t>
+        </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>

--- a/temp/BBVA_VISA_20250601.xlsx
+++ b/temp/BBVA_VISA_20250601.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>501580K MERPAGO*AXIONENERGY</t>
+          <t>MERPAGO*AXIONENERGY</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>571851* METROGAS SA DEB 040000136346</t>
+          <t>METROGAS SA DEB 040000136346</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>000001* EDENOR SA 000007691385963</t>
+          <t>EDENOR SA 000007691385963</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>002004* AA2000 PKG EZEIZA</t>
+          <t>AA2000 PKG EZEIZA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>115109K NETFLIX.COM 482190855 USD 8,53</t>
+          <t>NETFLIX.COM 482190855 USD 8,53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>000001* AUTOPISTAS URBAN 000000004488335</t>
+          <t>AUTOPISTAS URBAN 000000004488335</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>978934K MERPAGO*ESCUELADAVINCI</t>
+          <t>MERPAGO*ESCUELADAVINCI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>751873K MERPAGO*MODAXPRESSBA</t>
+          <t>MERPAGO*MODAXPRESSBA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>185665K MERPAGO*FARMACITY</t>
+          <t>MERPAGO*FARMACITY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>006376* PVS*THOMAS KITCHEN AND CO</t>
+          <t>PVS*THOMAS KITCHEN AND CO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>968318K MERPAGO*FARMACITY</t>
+          <t>MERPAGO*FARMACITY</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>977076K MERPAGO*FARMACITY</t>
+          <t>MERPAGO*FARMACITY</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>789835K POTTERY COFFEE DELI-POT</t>
+          <t>POTTERY COFFEE DELI-POT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>994344* BBVA SEGUROS A2052000420510-023-000</t>
+          <t>BBVA SEGUROS A2052000420510-023-000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>491046K PINCHOS-PINCHOS</t>
+          <t>PINCHOS-PINCHOS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>010998* TRIUNFO COOP D0000007681097-094-008</t>
+          <t>TRIUNFO COOP D0000007681097-094-008</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>007687K PAYU*AR*UBER</t>
+          <t>PAYU*AR*UBER</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>864313K MERPAGO*VEAEXPRESS</t>
+          <t>MERPAGO*VEAEXPRESS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>000001* AUTOPISTAS URBAN 000000004488335</t>
+          <t>AUTOPISTAS URBAN 000000004488335</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>287537K MERPAGO*SVMN</t>
+          <t>MERPAGO*SVMN</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>000001* SIRO -ROI SA 079001</t>
+          <t>SIRO -ROI SA 079001</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>312341K MERPAGO*HAVANNAFOODLI</t>
+          <t>MERPAGO*HAVANNAFOODLI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>595406K MERPAGO*MCDONALDSECOMM</t>
+          <t>MERPAGO*MCDONALDSECOMM</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>241004F Spotify USD 2,90</t>
+          <t>Spotify USD 2,90</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>539697K MERPAGO*PILISAR</t>
+          <t>MERPAGO*PILISAR</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>007115* CINEMARK</t>
+          <t>CINEMARK</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>626168K MERPAGO*SCANNAPIECO</t>
+          <t>MERPAGO*SCANNAPIECO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>004439K AXION BONPLAND</t>
+          <t>AXION BONPLAND</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>005932K PEDIDOSYA</t>
+          <t>PEDIDOSYA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>006726* SANDRULI SRL</t>
+          <t>SANDRULI SRL</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>140716* EXPERTA SEGURO0000037758111-015-000</t>
+          <t>EXPERTA SEGURO0000037758111-015-000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
